--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_64938_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_64938_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re39e1716059b4ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf59279d6b5ff4613"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4466</x:v>
+        <x:v>      0.4272</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3425</x:v>
+        <x:v>      0.3325</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3042</x:v>
+        <x:v>      0.2996</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3168</x:v>
+        <x:v>      0.3099</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2791</x:v>
+        <x:v>      0.2798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2667</x:v>
+        <x:v>      0.2704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3295</x:v>
+        <x:v>      0.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2791</x:v>
+        <x:v>      0.2798</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3680</x:v>
+        <x:v>      0.3541</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3170</x:v>
+        <x:v>      0.3108</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5239</x:v>
+        <x:v>      0.5058</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,133 +744,253 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.2345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2816</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2439</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3678</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3042</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3552</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2920</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2423</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.3421</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2421</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -750,126 +1005,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2796</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2299</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1931</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2296</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.1931</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>04/07/2026</x:t>
         </x:is>
       </x:c>
@@ -879,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3423</x:v>
+        <x:v>      0.3315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3042</x:v>
+        <x:v>      0.2996</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6531</x:v>
+        <x:v>      0.6480</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4840</x:v>
+        <x:v>      0.4665</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6283</x:v>
+        <x:v>      0.6270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6531</x:v>
+        <x:v>      0.6480</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4725</x:v>
+        <x:v>      0.4506</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5615</x:v>
+        <x:v>      0.5557</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_64938_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_64938_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf59279d6b5ff4613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R26282d088f45422f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3108</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1748</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2798</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4805</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3334</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3879</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
